--- a/results/02_taxa_assemblage/LDA_Method/ModelB_CorePeripheral/tables/site_eval_heldout.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelB_CorePeripheral/tables/site_eval_heldout.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,11 +483,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6917609145661818</v>
+        <v>0.1443578916117968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04319565258779271</v>
+        <v>4.085099451682151e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2650434328460256</v>
+        <v>0.8556380232887515</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6917609145661818</v>
+        <v>0.8556380232887515</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4267174817201563</v>
+        <v>0.7112801316769547</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -521,150 +521,36 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
       <c r="E3" t="n">
-        <v>0.2687837263580748</v>
+        <v>0.6461985272366956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2090586258329865</v>
+        <v>0.005331938135341549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5221576478089386</v>
+        <v>0.3484695346279628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5221576478089386</v>
+        <v>0.6461985272366956</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2533739214508637</v>
+        <v>0.2977289926087328</v>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>Held-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2329014762378219</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3695141408736883</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.3975843828884897</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3975843828884897</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.02807024201480135</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Held-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>S18</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.3094747352598711</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.2158256894385251</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.4746995753016038</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.4746995753016038</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.1652248400417327</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Held-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.2562442585369242</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.239365821992594</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5043899194704818</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5043899194704818</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.2481456609335577</v>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
